--- a/AAII_Financials/Quarterly/LTRN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LTRN_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/LTRN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LTRN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="92">
   <si>
     <t>LTRN</t>
   </si>
@@ -656,110 +656,117 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -826,8 +833,14 @@
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -894,8 +907,14 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -962,8 +981,14 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -988,76 +1013,84 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>2200</v>
+        <v>4300</v>
       </c>
       <c r="E12" s="3">
         <v>3600</v>
       </c>
       <c r="F12" s="3">
+        <v>2200</v>
+      </c>
+      <c r="G12" s="3">
+        <v>3600</v>
+      </c>
+      <c r="H12" s="3">
         <v>2600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>2300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>3000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>2700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>2200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>3000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>1200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>1300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>1300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>1000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>200</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,8 +1157,14 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1150,21 +1189,21 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
         <v>-100</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1177,11 +1216,11 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1192,8 +1231,14 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1260,8 +1305,14 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,76 +1334,84 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F17" s="3">
         <v>3500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>5200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>4300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>3800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>2100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>4400</v>
-      </c>
-      <c r="J17" s="3">
-        <v>4100</v>
-      </c>
-      <c r="K17" s="3">
-        <v>3500</v>
       </c>
       <c r="L17" s="3">
         <v>4100</v>
       </c>
       <c r="M17" s="3">
+        <v>3500</v>
+      </c>
+      <c r="N17" s="3">
+        <v>4100</v>
+      </c>
+      <c r="O17" s="3">
         <v>2400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>2500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>2900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>2400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>500</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1360,67 +1419,73 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="G18" s="3">
         <v>-5200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-4300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-3800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-2100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-4400</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-3500</v>
       </c>
       <c r="L18" s="3">
         <v>-4100</v>
       </c>
       <c r="M18" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="O18" s="3">
         <v>-2400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-2500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-2900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-2400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-500</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,8 +1510,10 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1454,7 +1521,7 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="F20" s="3">
         <v>400</v>
@@ -1463,29 +1530,29 @@
         <v>400</v>
       </c>
       <c r="H20" s="3">
-        <v>-100</v>
+        <v>400</v>
       </c>
       <c r="I20" s="3">
-        <v>-100</v>
+        <v>400</v>
       </c>
       <c r="J20" s="3">
         <v>-100</v>
       </c>
       <c r="K20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1504,17 +1571,23 @@
       <c r="U20" s="3">
         <v>0</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1522,67 +1595,73 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="G21" s="3">
         <v>-4700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-3900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-3400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-2300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-4500</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-3500</v>
       </c>
       <c r="L21" s="3">
         <v>-4100</v>
       </c>
       <c r="M21" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="O21" s="3">
         <v>-2300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-2500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-2900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-2400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-500</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1649,76 +1728,88 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-3200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-4700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-3900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-3400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-2300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-4500</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-3500</v>
       </c>
       <c r="L23" s="3">
         <v>-4100</v>
       </c>
       <c r="M23" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="N23" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="O23" s="3">
         <v>-2300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-2500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-2900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-2400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-500</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1785,8 +1876,14 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1950,162 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-3200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-4700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-3900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-3400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-2300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-4500</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-3500</v>
       </c>
       <c r="L26" s="3">
         <v>-4100</v>
       </c>
       <c r="M26" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="N26" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="O26" s="3">
         <v>-2300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-2500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-2900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-2400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-500</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-3200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-4700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-3900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-3400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-2300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-4500</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-3500</v>
       </c>
       <c r="L27" s="3">
         <v>-4100</v>
       </c>
       <c r="M27" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="N27" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="O27" s="3">
         <v>-2300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-2500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-2900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-2400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-500</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2172,14 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2246,14 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2320,14 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,8 +2394,14 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2270,7 +2409,7 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
-        <v>-400</v>
+        <v>-700</v>
       </c>
       <c r="F32" s="3">
         <v>-400</v>
@@ -2279,29 +2418,29 @@
         <v>-400</v>
       </c>
       <c r="H32" s="3">
-        <v>100</v>
+        <v>-400</v>
       </c>
       <c r="I32" s="3">
-        <v>100</v>
+        <v>-400</v>
       </c>
       <c r="J32" s="3">
         <v>100</v>
       </c>
       <c r="K32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L32" s="3">
+        <v>100</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -2320,85 +2459,97 @@
       <c r="U32" s="3">
         <v>0</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-3200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-4700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-3900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-3400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-2300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-4500</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-3500</v>
       </c>
       <c r="L33" s="3">
         <v>-4100</v>
       </c>
       <c r="M33" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="N33" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="O33" s="3">
         <v>-2300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-2500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-2900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-2400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-500</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2616,167 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-3200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-4700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-3900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-3400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-2300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-4500</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-3500</v>
       </c>
       <c r="L35" s="3">
         <v>-4100</v>
       </c>
       <c r="M35" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="N35" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="O35" s="3">
         <v>-2300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-2500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-2900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-2400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-500</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2801,10 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,62 +2829,64 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>21900</v>
+      </c>
+      <c r="F41" s="3">
         <v>25600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>28400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>32500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>37200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>39300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>43400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>46700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>51500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>54700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>61400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>81400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>19200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>20800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>23800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>600</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2726,47 +2899,53 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E42" s="3">
         <v>19400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
+        <v>19400</v>
+      </c>
+      <c r="G42" s="3">
         <v>19500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>19100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>18000</v>
-      </c>
-      <c r="H42" s="3">
-        <v>18600</v>
-      </c>
-      <c r="I42" s="3">
-        <v>18800</v>
       </c>
       <c r="J42" s="3">
         <v>18600</v>
       </c>
       <c r="K42" s="3">
+        <v>18800</v>
+      </c>
+      <c r="L42" s="3">
+        <v>18600</v>
+      </c>
+      <c r="M42" s="3">
         <v>19200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>19200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>18200</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2779,11 +2958,11 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
-      </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -2794,8 +2973,14 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2862,8 +3047,14 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2930,62 +3121,68 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F45" s="3">
         <v>2500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>3100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>3600</v>
-      </c>
-      <c r="G45" s="3">
-        <v>3500</v>
-      </c>
-      <c r="H45" s="3">
-        <v>4200</v>
       </c>
       <c r="I45" s="3">
         <v>3500</v>
       </c>
       <c r="J45" s="3">
+        <v>4200</v>
+      </c>
+      <c r="K45" s="3">
+        <v>3500</v>
+      </c>
+      <c r="L45" s="3">
         <v>2400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>2000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>2500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>2500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>100</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2998,62 +3195,68 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>39500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>43300</v>
+      </c>
+      <c r="F46" s="3">
         <v>47400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>51000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>55200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>58700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>62000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>65700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>67700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>72700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>76300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>82100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>82500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>20200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>22500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>25600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>800</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3066,8 +3269,14 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3134,47 +3343,53 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>200</v>
+      </c>
+      <c r="E48" s="3">
         <v>300</v>
-      </c>
-      <c r="E48" s="3">
-        <v>400</v>
       </c>
       <c r="F48" s="3">
         <v>300</v>
       </c>
       <c r="G48" s="3">
+        <v>400</v>
+      </c>
+      <c r="H48" s="3">
+        <v>300</v>
+      </c>
+      <c r="I48" s="3">
         <v>100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>100</v>
-      </c>
-      <c r="I48" s="3">
-        <v>200</v>
-      </c>
-      <c r="J48" s="3">
-        <v>200</v>
       </c>
       <c r="K48" s="3">
         <v>200</v>
       </c>
       <c r="L48" s="3">
+        <v>200</v>
+      </c>
+      <c r="M48" s="3">
+        <v>200</v>
+      </c>
+      <c r="N48" s="3">
         <v>300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>300</v>
       </c>
-      <c r="N48" s="3">
-        <v>0</v>
-      </c>
-      <c r="O48" s="3">
-        <v>0</v>
-      </c>
       <c r="P48" s="3">
         <v>0</v>
       </c>
@@ -3184,11 +3399,11 @@
       <c r="R48" s="3">
         <v>0</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+      <c r="T48" s="3">
+        <v>0</v>
       </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
@@ -3202,8 +3417,14 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3270,8 +3491,14 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3565,14 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,8 +3639,14 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3427,41 +3666,41 @@
         <v>0</v>
       </c>
       <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
         <v>600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1000</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
-      <c r="N52" s="3">
-        <v>0</v>
-      </c>
       <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3">
         <v>100</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
       <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
         <v>300</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3474,8 +3713,14 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,62 +3787,68 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>39700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>43600</v>
+      </c>
+      <c r="F54" s="3">
         <v>47800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>51400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>55500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>58800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>62200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>66400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>68400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>74000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>77600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>82400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>82500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>20400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>22500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>25600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1000</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3610,8 +3861,14 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3893,10 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,62 +3921,64 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F57" s="3">
         <v>2100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>3000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>5200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>2200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>400</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3730,8 +3991,14 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3771,21 +4038,21 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
+      <c r="P58" s="3">
+        <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3">
         <v>100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>100</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3798,8 +4065,14 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3810,10 +4083,10 @@
         <v>200</v>
       </c>
       <c r="F59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H59" s="3">
         <v>100</v>
@@ -3822,35 +4095,35 @@
         <v>100</v>
       </c>
       <c r="J59" s="3">
+        <v>100</v>
+      </c>
+      <c r="K59" s="3">
+        <v>100</v>
+      </c>
+      <c r="L59" s="3">
         <v>200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1600</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3">
         <v>1700</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3866,62 +4139,68 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F60" s="3">
         <v>2300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2800</v>
-      </c>
-      <c r="H60" s="3">
-        <v>3100</v>
-      </c>
-      <c r="I60" s="3">
-        <v>5300</v>
       </c>
       <c r="J60" s="3">
         <v>3100</v>
       </c>
       <c r="K60" s="3">
+        <v>5300</v>
+      </c>
+      <c r="L60" s="3">
+        <v>3100</v>
+      </c>
+      <c r="M60" s="3">
         <v>2300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>2700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>2300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>500</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3934,8 +4213,14 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3970,10 +4255,10 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P61" s="3">
         <v>100</v>
@@ -3982,10 +4267,10 @@
         <v>100</v>
       </c>
       <c r="R61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T61" s="3">
         <v>0</v>
@@ -4002,25 +4287,31 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3">
         <v>100</v>
-      </c>
-      <c r="E62" s="3">
-        <v>200</v>
       </c>
       <c r="F62" s="3">
         <v>100</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I62" s="3">
         <v>0</v>
@@ -4029,19 +4320,19 @@
         <v>0</v>
       </c>
       <c r="K62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M62" s="3">
         <v>100</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
+      <c r="N62" s="3">
+        <v>100</v>
+      </c>
+      <c r="O62" s="3">
+        <v>100</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
@@ -4055,11 +4346,11 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T62" s="3">
-        <v>0</v>
-      </c>
-      <c r="U62" s="3">
-        <v>0</v>
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V62" s="3">
         <v>0</v>
@@ -4070,8 +4361,14 @@
       <c r="X62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4435,14 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4509,14 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,62 +4583,68 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F66" s="3">
         <v>2400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>3200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>2900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>2800</v>
-      </c>
-      <c r="H66" s="3">
-        <v>3100</v>
-      </c>
-      <c r="I66" s="3">
-        <v>5300</v>
       </c>
       <c r="J66" s="3">
         <v>3100</v>
       </c>
       <c r="K66" s="3">
+        <v>5300</v>
+      </c>
+      <c r="L66" s="3">
+        <v>3100</v>
+      </c>
+      <c r="M66" s="3">
         <v>2400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>2800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>2400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>500</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4342,8 +4657,14 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4689,10 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4759,14 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4833,14 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4572,8 +4907,14 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,62 +4981,68 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-60700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-55200</v>
+      </c>
+      <c r="F72" s="3">
         <v>-51100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-47900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-43200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-39300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-35900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-33600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-29100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-25000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-21500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-17400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-15100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-12700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-8100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-7200</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4708,8 +5055,14 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +5129,14 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5203,14 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,62 +5277,68 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>35800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>40900</v>
+      </c>
+      <c r="F76" s="3">
         <v>45400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>48300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>52600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>56000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>59000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>61100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>65300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>71600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>75700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>79600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>81700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>19700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>21600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>23200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>500</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4980,8 +5351,14 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5425,167 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-3200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-4700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-3900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-3400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-2300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-4500</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-3500</v>
       </c>
       <c r="L81" s="3">
         <v>-4100</v>
       </c>
       <c r="M81" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="N81" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="O81" s="3">
         <v>-2300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-2500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-2900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-2400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-500</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,8 +5610,10 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5274,17 +5671,23 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+      <c r="W83" s="3">
+        <v>0</v>
       </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5754,14 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5828,14 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5902,14 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5976,14 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,76 +6050,88 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F89" s="3">
         <v>-3600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-3600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-3800</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-4000</v>
       </c>
       <c r="I89" s="3">
         <v>-2700</v>
       </c>
       <c r="J89" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="K89" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="L89" s="3">
         <v>-3300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-2000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-4700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-1700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-2100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-1600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-2100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-400</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,8 +6156,10 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5749,32 +6190,32 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
@@ -5785,8 +6226,14 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6300,14 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,64 +6374,70 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E94" s="3">
+        <v>300</v>
+      </c>
+      <c r="F94" s="3">
         <v>200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-1000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-1000</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
+      <c r="U94" s="3">
+        <v>0</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
@@ -5989,8 +6448,14 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6480,10 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6083,8 +6550,14 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6624,14 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6698,14 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,16 +6772,22 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="F100" s="3">
         <v>0</v>
@@ -6311,52 +6802,58 @@
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-2200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-900</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>64300</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>-100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>23700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>2900</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>1900</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6381,11 +6878,11 @@
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
@@ -6399,11 +6896,11 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S101" s="3">
         <v>0</v>
@@ -6423,72 +6920,84 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="F102" s="3">
         <v>-3400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-4100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-4700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-2100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-4100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-3300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-5300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-3100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-5700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-20000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>62100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-1600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>23200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>1400</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LTRN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LTRN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="92">
   <si>
     <t>LTRN</t>
   </si>
@@ -656,117 +656,121 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -839,8 +843,11 @@
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -913,8 +920,11 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -987,8 +997,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1015,82 +1028,86 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E12" s="3">
         <v>4300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>3600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>3600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1200</v>
-      </c>
-      <c r="P12" s="3">
-        <v>1300</v>
       </c>
       <c r="Q12" s="3">
         <v>1300</v>
       </c>
       <c r="R12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="S12" s="3">
         <v>600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>200</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1163,8 +1180,11 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1195,18 +1215,18 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>-100</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1222,8 +1242,8 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1237,8 +1257,11 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1311,8 +1334,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1336,82 +1362,86 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E17" s="3">
         <v>5700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>500</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1419,73 +1449,76 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-4900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-5200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-4300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-500</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1512,8 +1545,9 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1521,10 +1555,10 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>300</v>
+      </c>
+      <c r="F20" s="3">
         <v>700</v>
-      </c>
-      <c r="F20" s="3">
-        <v>400</v>
       </c>
       <c r="G20" s="3">
         <v>400</v>
@@ -1536,7 +1570,7 @@
         <v>400</v>
       </c>
       <c r="J20" s="3">
-        <v>-100</v>
+        <v>400</v>
       </c>
       <c r="K20" s="3">
         <v>-100</v>
@@ -1545,16 +1579,16 @@
         <v>-100</v>
       </c>
       <c r="M20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O20" s="3">
         <v>100</v>
       </c>
       <c r="P20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -1577,8 +1611,8 @@
       <c r="W20" s="3">
         <v>0</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
+      <c r="X20" s="3">
+        <v>0</v>
       </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
@@ -1586,8 +1620,11 @@
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1595,73 +1632,76 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="F21" s="3">
         <v>-4200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-4700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-3900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-3400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-4500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-4100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-3500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-4100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-500</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1734,82 +1774,88 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-500</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1882,8 +1928,11 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1956,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-500</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-500</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2178,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2252,8 +2313,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2326,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2400,8 +2467,11 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2409,10 +2479,10 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F32" s="3">
         <v>-700</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-400</v>
       </c>
       <c r="G32" s="3">
         <v>-400</v>
@@ -2424,7 +2494,7 @@
         <v>-400</v>
       </c>
       <c r="J32" s="3">
-        <v>100</v>
+        <v>-400</v>
       </c>
       <c r="K32" s="3">
         <v>100</v>
@@ -2433,16 +2503,16 @@
         <v>100</v>
       </c>
       <c r="M32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O32" s="3">
         <v>-100</v>
       </c>
       <c r="P32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
@@ -2465,8 +2535,8 @@
       <c r="W32" s="3">
         <v>0</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
+      <c r="X32" s="3">
+        <v>0</v>
       </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
@@ -2474,82 +2544,88 @@
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-4200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-4100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-500</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2622,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-4200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-4100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-500</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2803,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2831,65 +2917,66 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E41" s="3">
         <v>18400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>21900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>25600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>28400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>32500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>37200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>39300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>43400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>46700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>51500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>54700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>61400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>81400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>19200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>20800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>23800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>600</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2905,50 +2992,53 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E42" s="3">
         <v>20000</v>
-      </c>
-      <c r="E42" s="3">
-        <v>19400</v>
       </c>
       <c r="F42" s="3">
         <v>19400</v>
       </c>
       <c r="G42" s="3">
+        <v>19400</v>
+      </c>
+      <c r="H42" s="3">
         <v>19500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>19100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>18000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>18600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>18800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>18600</v>
-      </c>
-      <c r="M42" s="3">
-        <v>19200</v>
       </c>
       <c r="N42" s="3">
         <v>19200</v>
       </c>
       <c r="O42" s="3">
+        <v>19200</v>
+      </c>
+      <c r="P42" s="3">
         <v>18200</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2964,8 +3054,8 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -2979,8 +3069,11 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3053,8 +3146,11 @@
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3127,65 +3223,68 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2000</v>
-      </c>
-      <c r="N45" s="3">
-        <v>2500</v>
       </c>
       <c r="O45" s="3">
         <v>2500</v>
       </c>
       <c r="P45" s="3">
+        <v>2500</v>
+      </c>
+      <c r="Q45" s="3">
         <v>1100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>100</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3201,65 +3300,68 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E46" s="3">
         <v>39500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>43300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>47400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>51000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>55200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>58700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>62000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>65700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>67700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>72700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>76300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>82100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>82500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>20200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>22500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>25600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>800</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3275,8 +3377,11 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3349,34 +3454,37 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>300</v>
+      </c>
+      <c r="E48" s="3">
         <v>200</v>
-      </c>
-      <c r="E48" s="3">
-        <v>300</v>
       </c>
       <c r="F48" s="3">
         <v>300</v>
       </c>
       <c r="G48" s="3">
+        <v>300</v>
+      </c>
+      <c r="H48" s="3">
         <v>400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>300</v>
-      </c>
-      <c r="I48" s="3">
-        <v>100</v>
       </c>
       <c r="J48" s="3">
         <v>100</v>
       </c>
       <c r="K48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L48" s="3">
         <v>200</v>
@@ -3385,13 +3493,13 @@
         <v>200</v>
       </c>
       <c r="N48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O48" s="3">
         <v>300</v>
       </c>
       <c r="P48" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Q48" s="3">
         <v>0</v>
@@ -3405,8 +3513,8 @@
       <c r="T48" s="3">
         <v>0</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
+      <c r="U48" s="3">
+        <v>0</v>
       </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
@@ -3423,8 +3531,11 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3497,8 +3608,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3571,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3645,8 +3762,11 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3672,38 +3792,38 @@
         <v>0</v>
       </c>
       <c r="K52" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="L52" s="3">
         <v>600</v>
       </c>
       <c r="M52" s="3">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="N52" s="3">
         <v>1000</v>
       </c>
       <c r="O52" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
       </c>
       <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
         <v>100</v>
       </c>
-      <c r="R52" s="3">
-        <v>0</v>
-      </c>
       <c r="S52" s="3">
         <v>0</v>
       </c>
       <c r="T52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3">
         <v>300</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3719,8 +3839,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3793,65 +3916,68 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>35600</v>
+      </c>
+      <c r="E54" s="3">
         <v>39700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>43600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>47800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>51400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>55500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>58800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>62200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>66400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>68400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>74000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>77600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>82400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>82500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>20400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>22500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>25600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1000</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3867,8 +3993,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3895,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3923,65 +4053,66 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E57" s="3">
         <v>3800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2900</v>
-      </c>
-      <c r="H57" s="3">
-        <v>2700</v>
       </c>
       <c r="I57" s="3">
         <v>2700</v>
       </c>
       <c r="J57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="K57" s="3">
         <v>3000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>400</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3997,8 +4128,11 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4044,17 +4178,17 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S58" s="3">
-        <v>100</v>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T58" s="3">
         <v>100</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
+      <c r="U58" s="3">
+        <v>100</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
@@ -4071,8 +4205,11 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4089,7 +4226,7 @@
         <v>200</v>
       </c>
       <c r="H59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I59" s="3">
         <v>100</v>
@@ -4101,32 +4238,32 @@
         <v>100</v>
       </c>
       <c r="L59" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M59" s="3">
         <v>200</v>
       </c>
       <c r="N59" s="3">
+        <v>200</v>
+      </c>
+      <c r="O59" s="3">
         <v>100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1600</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S59" s="3">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T59" s="3">
         <v>1700</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4145,65 +4282,68 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E60" s="3">
         <v>4000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3000</v>
-      </c>
-      <c r="H60" s="3">
-        <v>2800</v>
       </c>
       <c r="I60" s="3">
         <v>2800</v>
       </c>
       <c r="J60" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K60" s="3">
         <v>3100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>500</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4219,8 +4359,11 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4261,7 +4404,7 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q61" s="3">
         <v>100</v>
@@ -4273,7 +4416,7 @@
         <v>100</v>
       </c>
       <c r="T61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U61" s="3">
         <v>0</v>
@@ -4293,29 +4436,32 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F62" s="3">
         <v>100</v>
       </c>
       <c r="G62" s="3">
+        <v>100</v>
+      </c>
+      <c r="H62" s="3">
         <v>200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>100</v>
       </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
       <c r="J62" s="3">
         <v>0</v>
       </c>
@@ -4326,7 +4472,7 @@
         <v>0</v>
       </c>
       <c r="M62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N62" s="3">
         <v>100</v>
@@ -4334,8 +4480,8 @@
       <c r="O62" s="3">
         <v>100</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
+      <c r="P62" s="3">
+        <v>100</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
@@ -4352,8 +4498,8 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V62" s="3">
-        <v>0</v>
+      <c r="V62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W62" s="3">
         <v>0</v>
@@ -4367,8 +4513,11 @@
       <c r="Z62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4441,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4515,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4589,65 +4744,68 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E66" s="3">
         <v>4000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>500</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4663,8 +4821,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4691,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4765,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4839,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4913,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4987,65 +5158,68 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-65600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-60700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-55200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-51100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-47900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-43200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-39300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-35900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-33600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-29100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-25000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-21500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-17400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-15100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-12700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-9800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-8100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-7200</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5061,8 +5235,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5135,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5209,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5283,65 +5466,68 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E76" s="3">
         <v>35800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>40900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>45400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>48300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>52600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>56000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>59000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>61100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>65300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>71600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>75700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>79600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>81700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>19700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>21600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>23200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>500</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5357,8 +5543,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5431,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-4200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-4100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-500</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5612,8 +5810,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5677,8 +5876,8 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
+      <c r="X83" s="3">
+        <v>0</v>
       </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
@@ -5686,8 +5885,11 @@
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5760,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5834,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5908,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5982,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6056,73 +6270,76 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3400</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-3600</v>
       </c>
       <c r="G89" s="3">
         <v>-3600</v>
       </c>
       <c r="H89" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="I89" s="3">
         <v>-3800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2100</v>
-      </c>
-      <c r="V89" s="3">
-        <v>-400</v>
       </c>
       <c r="W89" s="3">
         <v>-400</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
+      <c r="X89" s="3">
+        <v>-400</v>
       </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
@@ -6130,8 +6347,11 @@
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6158,8 +6378,9 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6196,29 +6417,29 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
@@ -6232,8 +6453,11 @@
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6306,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6380,67 +6607,70 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1000</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
+      <c r="S94" s="3">
+        <v>0</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
@@ -6454,8 +6684,11 @@
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6482,8 +6715,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6556,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6630,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6704,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6778,20 +7021,23 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-500</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
@@ -6808,52 +7054,55 @@
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-2200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-900</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>64300</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>-100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>23700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2900</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>1900</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6884,8 +7133,8 @@
       <c r="L101" s="3">
         <v>0</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
+      <c r="M101" s="3">
+        <v>0</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
@@ -6902,8 +7151,8 @@
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
+      <c r="S101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T101" s="3">
         <v>0</v>
@@ -6926,78 +7175,84 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-3600</v>
+        <v>-5400</v>
       </c>
       <c r="E102" s="3">
         <v>-3600</v>
       </c>
       <c r="F102" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="G102" s="3">
         <v>-3400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-5700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-20000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>62100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>23200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1400</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LTRN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LTRN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="92">
   <si>
     <t>LTRN</t>
   </si>
@@ -656,144 +656,148 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -846,8 +850,11 @@
       <c r="AA8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -923,8 +930,11 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1000,8 +1010,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1029,85 +1042,89 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E12" s="3">
         <v>3900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1200</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>1300</v>
       </c>
       <c r="R12" s="3">
         <v>1300</v>
       </c>
       <c r="S12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="T12" s="3">
         <v>600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>200</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1183,8 +1200,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1194,8 +1214,8 @@
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
@@ -1206,8 +1226,8 @@
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -1218,18 +1238,18 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-100</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1245,8 +1265,8 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1260,8 +1280,11 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1337,8 +1360,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,162 +1389,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E17" s="3">
         <v>5400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>500</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-5200</v>
       </c>
       <c r="E18" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-5700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-4900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-5200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-4300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-500</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1546,34 +1579,35 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>-500</v>
       </c>
       <c r="E20" s="3">
-        <v>300</v>
+        <v>-300</v>
       </c>
       <c r="F20" s="3">
-        <v>700</v>
+        <v>-100</v>
       </c>
       <c r="G20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K20" s="3">
         <v>400</v>
-      </c>
-      <c r="H20" s="3">
-        <v>400</v>
-      </c>
-      <c r="I20" s="3">
-        <v>400</v>
-      </c>
-      <c r="J20" s="3">
-        <v>400</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-100</v>
       </c>
       <c r="L20" s="3">
         <v>-100</v>
@@ -1582,16 +1616,16 @@
         <v>-100</v>
       </c>
       <c r="N20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P20" s="3">
         <v>100</v>
       </c>
       <c r="Q20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -1614,8 +1648,8 @@
       <c r="X20" s="3">
         <v>0</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
+      <c r="Y20" s="3">
+        <v>0</v>
       </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
@@ -1623,108 +1657,114 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-4700</v>
       </c>
       <c r="E21" s="3">
-        <v>-5400</v>
+        <v>-5100</v>
       </c>
       <c r="F21" s="3">
-        <v>-4200</v>
+        <v>-5600</v>
       </c>
       <c r="G21" s="3">
-        <v>-3200</v>
+        <v>-4400</v>
       </c>
       <c r="H21" s="3">
-        <v>-4700</v>
+        <v>-3400</v>
       </c>
       <c r="I21" s="3">
-        <v>-3900</v>
+        <v>-4900</v>
       </c>
       <c r="J21" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="K21" s="3">
         <v>-3400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-4500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-4100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-3500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-4100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-500</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1777,108 +1817,114 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-4700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-500</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1931,8 +1977,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,162 +2057,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-500</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-500</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2316,8 +2377,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,34 +2537,37 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>500</v>
       </c>
       <c r="E32" s="3">
-        <v>-300</v>
+        <v>300</v>
       </c>
       <c r="F32" s="3">
-        <v>-700</v>
+        <v>100</v>
       </c>
       <c r="G32" s="3">
+        <v>400</v>
+      </c>
+      <c r="H32" s="3">
+        <v>100</v>
+      </c>
+      <c r="I32" s="3">
+        <v>300</v>
+      </c>
+      <c r="J32" s="3">
+        <v>200</v>
+      </c>
+      <c r="K32" s="3">
         <v>-400</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="K32" s="3">
-        <v>100</v>
       </c>
       <c r="L32" s="3">
         <v>100</v>
@@ -2506,16 +2576,16 @@
         <v>100</v>
       </c>
       <c r="N32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P32" s="3">
         <v>-100</v>
       </c>
       <c r="Q32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -2538,8 +2608,8 @@
       <c r="X32" s="3">
         <v>0</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
+      <c r="Y32" s="3">
+        <v>0</v>
       </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
@@ -2547,85 +2617,91 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-4500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-4100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-500</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,167 +2777,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-4500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-4100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-500</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,68 +3004,69 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E41" s="3">
         <v>13000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>18400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>21900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>25600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>28400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>32500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>37200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>39300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>43400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>46700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>51500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>54700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>61400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>81400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>19200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>20800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>23800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>600</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2995,53 +3082,56 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E42" s="3">
         <v>20300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>20000</v>
-      </c>
-      <c r="F42" s="3">
-        <v>19400</v>
       </c>
       <c r="G42" s="3">
         <v>19400</v>
       </c>
       <c r="H42" s="3">
+        <v>19400</v>
+      </c>
+      <c r="I42" s="3">
         <v>19500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>19100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>18000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>18600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>18800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>18600</v>
-      </c>
-      <c r="N42" s="3">
-        <v>19200</v>
       </c>
       <c r="O42" s="3">
         <v>19200</v>
       </c>
       <c r="P42" s="3">
+        <v>19200</v>
+      </c>
+      <c r="Q42" s="3">
         <v>18200</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3057,8 +3147,8 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
+      <c r="W42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
@@ -3072,31 +3162,34 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+        <v>900</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3149,31 +3242,34 @@
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3226,68 +3322,71 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>700</v>
+      </c>
+      <c r="E45" s="3">
+        <v>900</v>
+      </c>
+      <c r="F45" s="3">
+        <v>400</v>
+      </c>
+      <c r="G45" s="3">
+        <v>700</v>
+      </c>
+      <c r="H45" s="3">
+        <v>800</v>
+      </c>
+      <c r="I45" s="3">
+        <v>700</v>
+      </c>
+      <c r="J45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K45" s="3">
+        <v>3500</v>
+      </c>
+      <c r="L45" s="3">
+        <v>4200</v>
+      </c>
+      <c r="M45" s="3">
+        <v>3500</v>
+      </c>
+      <c r="N45" s="3">
+        <v>2400</v>
+      </c>
+      <c r="O45" s="3">
         <v>2000</v>
-      </c>
-      <c r="E45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="F45" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>2500</v>
-      </c>
-      <c r="H45" s="3">
-        <v>3100</v>
-      </c>
-      <c r="I45" s="3">
-        <v>3600</v>
-      </c>
-      <c r="J45" s="3">
-        <v>3500</v>
-      </c>
-      <c r="K45" s="3">
-        <v>4200</v>
-      </c>
-      <c r="L45" s="3">
-        <v>3500</v>
-      </c>
-      <c r="M45" s="3">
-        <v>2400</v>
-      </c>
-      <c r="N45" s="3">
-        <v>2000</v>
-      </c>
-      <c r="O45" s="3">
-        <v>2500</v>
       </c>
       <c r="P45" s="3">
         <v>2500</v>
       </c>
       <c r="Q45" s="3">
+        <v>2500</v>
+      </c>
+      <c r="R45" s="3">
         <v>1100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>100</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3303,68 +3402,71 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E46" s="3">
         <v>35300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>39500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>43300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>47400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>51000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>55200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>58700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>62000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>65700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>67700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>72700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>76300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>82100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>82500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>20200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>22500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>25600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>800</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3380,31 +3482,34 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3457,8 +3562,11 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3466,28 +3574,28 @@
         <v>300</v>
       </c>
       <c r="E48" s="3">
+        <v>300</v>
+      </c>
+      <c r="F48" s="3">
         <v>200</v>
-      </c>
-      <c r="F48" s="3">
-        <v>300</v>
       </c>
       <c r="G48" s="3">
         <v>300</v>
       </c>
       <c r="H48" s="3">
+        <v>300</v>
+      </c>
+      <c r="I48" s="3">
         <v>400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>300</v>
-      </c>
-      <c r="J48" s="3">
-        <v>100</v>
       </c>
       <c r="K48" s="3">
         <v>100</v>
       </c>
       <c r="L48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M48" s="3">
         <v>200</v>
@@ -3496,13 +3604,13 @@
         <v>200</v>
       </c>
       <c r="O48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="P48" s="3">
         <v>300</v>
       </c>
       <c r="Q48" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
@@ -3516,8 +3624,8 @@
       <c r="U48" s="3">
         <v>0</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
+      <c r="V48" s="3">
+        <v>0</v>
       </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
@@ -3534,8 +3642,11 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3611,8 +3722,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,8 +3882,11 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3795,38 +3915,38 @@
         <v>0</v>
       </c>
       <c r="L52" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="M52" s="3">
         <v>600</v>
       </c>
       <c r="N52" s="3">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="O52" s="3">
         <v>1000</v>
       </c>
       <c r="P52" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Q52" s="3">
         <v>0</v>
       </c>
       <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
         <v>100</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
-      </c>
       <c r="T52" s="3">
         <v>0</v>
       </c>
       <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3">
         <v>300</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3842,8 +3962,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,68 +4042,71 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E54" s="3">
         <v>35600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>39700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>43600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>47800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>51400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>55500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>58800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>62200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>66400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>68400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>74000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>77600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>82400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>82500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>20400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>22500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>25600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1000</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3996,8 +4122,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,68 +4184,69 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4400</v>
+        <v>2500</v>
       </c>
       <c r="E57" s="3">
-        <v>3800</v>
+        <v>2400</v>
       </c>
       <c r="F57" s="3">
-        <v>2500</v>
+        <v>1600</v>
       </c>
       <c r="G57" s="3">
-        <v>2100</v>
+        <v>900</v>
       </c>
       <c r="H57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="L57" s="3">
+        <v>3000</v>
+      </c>
+      <c r="M57" s="3">
+        <v>5200</v>
+      </c>
+      <c r="N57" s="3">
         <v>2900</v>
       </c>
-      <c r="I57" s="3">
-        <v>2700</v>
-      </c>
-      <c r="J57" s="3">
-        <v>2700</v>
-      </c>
-      <c r="K57" s="3">
-        <v>3000</v>
-      </c>
-      <c r="L57" s="3">
-        <v>5200</v>
-      </c>
-      <c r="M57" s="3">
-        <v>2900</v>
-      </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>400</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4131,31 +4262,34 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4181,17 +4315,17 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T58" s="3">
-        <v>100</v>
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U58" s="3">
         <v>100</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
+      <c r="V58" s="3">
+        <v>100</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
@@ -4208,31 +4342,34 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="E59" s="3">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="F59" s="3">
-        <v>200</v>
+        <v>2200</v>
       </c>
       <c r="G59" s="3">
-        <v>200</v>
+        <v>1600</v>
       </c>
       <c r="H59" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="I59" s="3">
-        <v>100</v>
+        <v>1200</v>
       </c>
       <c r="J59" s="3">
-        <v>100</v>
+        <v>1500</v>
       </c>
       <c r="K59" s="3">
         <v>100</v>
@@ -4241,32 +4378,32 @@
         <v>100</v>
       </c>
       <c r="M59" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N59" s="3">
         <v>200</v>
       </c>
       <c r="O59" s="3">
+        <v>200</v>
+      </c>
+      <c r="P59" s="3">
         <v>100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1600</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T59" s="3">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U59" s="3">
         <v>1700</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4285,68 +4422,71 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E60" s="3">
         <v>4600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3000</v>
-      </c>
-      <c r="I60" s="3">
-        <v>2800</v>
       </c>
       <c r="J60" s="3">
         <v>2800</v>
       </c>
       <c r="K60" s="3">
+        <v>2800</v>
+      </c>
+      <c r="L60" s="3">
         <v>3100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>500</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4362,31 +4502,34 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4407,7 +4550,7 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R61" s="3">
         <v>100</v>
@@ -4419,7 +4562,7 @@
         <v>100</v>
       </c>
       <c r="U61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V61" s="3">
         <v>0</v>
@@ -4439,31 +4582,34 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>100</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>100</v>
-      </c>
-      <c r="G62" s="3">
-        <v>100</v>
-      </c>
-      <c r="H62" s="3">
-        <v>200</v>
-      </c>
-      <c r="I62" s="3">
-        <v>100</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -4475,7 +4621,7 @@
         <v>0</v>
       </c>
       <c r="N62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O62" s="3">
         <v>100</v>
@@ -4483,8 +4629,8 @@
       <c r="P62" s="3">
         <v>100</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
+      <c r="Q62" s="3">
+        <v>100</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
@@ -4501,8 +4647,8 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W62" s="3">
-        <v>0</v>
+      <c r="W62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X62" s="3">
         <v>0</v>
@@ -4516,8 +4662,11 @@
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,68 +4902,71 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E66" s="3">
         <v>4700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>500</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4824,8 +4982,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5084,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,68 +5332,71 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-70200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-65600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-60700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-55200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-51100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-47900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-43200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-39300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-35900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-33600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-29100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-25000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-21500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-17400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-15100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-12700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-9800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-8100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-7200</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5238,8 +5412,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,68 +5652,71 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E76" s="3">
         <v>30900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>35800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>40900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>45400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>48300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>52600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>56000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>59000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>61100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>65300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>71600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>75700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>79600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>81700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>19700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>21600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>23200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>500</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5546,8 +5732,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,167 +5812,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-4500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-4100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-500</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,8 +6009,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5826,7 +6025,7 @@
         <v>0</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H83" s="3">
         <v>0</v>
@@ -5879,8 +6078,8 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
+      <c r="Y83" s="3">
+        <v>0</v>
       </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
@@ -5888,8 +6087,11 @@
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,76 +6487,79 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-5200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3400</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-3600</v>
       </c>
       <c r="H89" s="3">
         <v>-3600</v>
       </c>
       <c r="I89" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="J89" s="3">
         <v>-3800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-4700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2100</v>
-      </c>
-      <c r="W89" s="3">
-        <v>-400</v>
       </c>
       <c r="X89" s="3">
         <v>-400</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
+      <c r="Y89" s="3">
+        <v>-400</v>
       </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
@@ -6350,8 +6567,11 @@
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,8 +6599,9 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6420,29 +6641,29 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="R91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
+      <c r="T91" s="3">
+        <v>0</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
@@ -6456,8 +6677,11 @@
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,70 +6837,73 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1000</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
+      <c r="R94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
+      <c r="T94" s="3">
+        <v>0</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W94" s="3">
+        <v>0</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
@@ -6687,8 +6917,11 @@
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,31 +6949,32 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6793,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,8 +7267,11 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7033,22 +7279,22 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-500</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -7057,52 +7303,55 @@
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-2200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-900</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>64300</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>-100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>23700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2900</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>1900</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7136,8 +7385,8 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
+      <c r="N101" s="3">
+        <v>0</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
@@ -7154,8 +7403,8 @@
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
+      <c r="T101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
@@ -7178,81 +7427,87 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5400</v>
-      </c>
-      <c r="E102" s="3">
-        <v>-3600</v>
       </c>
       <c r="F102" s="3">
         <v>-3600</v>
       </c>
       <c r="G102" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="H102" s="3">
         <v>-3400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-5700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>62100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>23200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1400</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LTRN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LTRN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="92">
   <si>
     <t>LTRN</t>
   </si>
@@ -656,125 +656,132 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -799,11 +806,11 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -853,8 +860,14 @@
       <c r="AB8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -933,8 +946,14 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1013,8 +1032,14 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1043,88 +1068,96 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E12" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F12" s="3">
         <v>3700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>3900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>4300</v>
-      </c>
-      <c r="G12" s="3">
-        <v>3600</v>
-      </c>
-      <c r="H12" s="3">
-        <v>2200</v>
       </c>
       <c r="I12" s="3">
         <v>3600</v>
       </c>
       <c r="J12" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K12" s="3">
+        <v>3600</v>
+      </c>
+      <c r="L12" s="3">
         <v>2600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>2300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>3000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>2700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>2200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>3000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>1200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>1300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>1300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>1000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>200</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1203,37 +1236,43 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="E14" s="3">
+        <v>200</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
@@ -1241,21 +1280,21 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3">
         <v>-100</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1268,11 +1307,11 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1283,8 +1322,14 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1363,8 +1408,14 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,168 +1441,182 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F17" s="3">
         <v>5200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>5400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>5700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>4900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>3500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>5200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>4300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>3800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>2100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>4400</v>
-      </c>
-      <c r="N17" s="3">
-        <v>4100</v>
-      </c>
-      <c r="O17" s="3">
-        <v>3500</v>
       </c>
       <c r="P17" s="3">
         <v>4100</v>
       </c>
       <c r="Q17" s="3">
+        <v>3500</v>
+      </c>
+      <c r="R17" s="3">
+        <v>4100</v>
+      </c>
+      <c r="S17" s="3">
         <v>2400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>2500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>2900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>2400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>500</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-5200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-5400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-5700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-4900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-3500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-5200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-4300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-3800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-2100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-4400</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-3500</v>
       </c>
       <c r="P18" s="3">
         <v>-4100</v>
       </c>
       <c r="Q18" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="R18" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="S18" s="3">
         <v>-2400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-2500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-2900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-1700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-2400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-500</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,59 +1645,61 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="3">
         <v>-500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-300</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-400</v>
       </c>
       <c r="H20" s="3">
         <v>-100</v>
       </c>
       <c r="I20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>400</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-100</v>
       </c>
       <c r="N20" s="3">
         <v>-100</v>
       </c>
       <c r="O20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -1651,17 +1718,23 @@
       <c r="Y20" s="3">
         <v>0</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>0</v>
       </c>
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1669,79 +1742,85 @@
         <v>-4700</v>
       </c>
       <c r="E21" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="G21" s="3">
         <v>-5100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-5600</v>
       </c>
-      <c r="G21" s="3">
-        <v>-4400</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="J21" s="3">
         <v>-3400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-4900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-4000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-3400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-2300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-4500</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-3500</v>
       </c>
       <c r="P21" s="3">
         <v>-4100</v>
       </c>
       <c r="Q21" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="R21" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="S21" s="3">
         <v>-2300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-2500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-2900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-1700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-2400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-500</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1766,11 +1845,11 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1820,8 +1899,14 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1829,79 +1914,85 @@
         <v>-4500</v>
       </c>
       <c r="E23" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="F23" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="G23" s="3">
         <v>-5000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-5400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-4200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-3200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-4700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-3900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-3400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-2300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-4500</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-3500</v>
       </c>
       <c r="P23" s="3">
         <v>-4100</v>
       </c>
       <c r="Q23" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="R23" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="S23" s="3">
         <v>-2300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-2500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-2900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-1700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-2400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-500</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1926,11 +2017,11 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1980,8 +2071,14 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,8 +2157,14 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2069,79 +2172,85 @@
         <v>-4500</v>
       </c>
       <c r="E26" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="F26" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="G26" s="3">
         <v>-5000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-5400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-4200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-3200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-4700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-3900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-3400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-2300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-4500</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-3500</v>
       </c>
       <c r="P26" s="3">
         <v>-4100</v>
       </c>
       <c r="Q26" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="R26" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="S26" s="3">
         <v>-2300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-2500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-2900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-1700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-2400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-500</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2149,79 +2258,85 @@
         <v>-4500</v>
       </c>
       <c r="E27" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="G27" s="3">
         <v>-5000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-5400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-4200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-3200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-4700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-3900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-3400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-2300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-4500</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-3500</v>
       </c>
       <c r="P27" s="3">
         <v>-4100</v>
       </c>
       <c r="Q27" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="R27" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="S27" s="3">
         <v>-2300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-2500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-2900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-1700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-2400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-500</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2415,14 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2380,8 +2501,14 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2587,14 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,59 +2673,65 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3">
+        <v>100</v>
+      </c>
+      <c r="F32" s="3">
         <v>500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>300</v>
-      </c>
-      <c r="F32" s="3">
-        <v>100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>400</v>
       </c>
       <c r="H32" s="3">
         <v>100</v>
       </c>
       <c r="I32" s="3">
+        <v>400</v>
+      </c>
+      <c r="J32" s="3">
+        <v>100</v>
+      </c>
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-400</v>
-      </c>
-      <c r="L32" s="3">
-        <v>100</v>
-      </c>
-      <c r="M32" s="3">
-        <v>100</v>
       </c>
       <c r="N32" s="3">
         <v>100</v>
       </c>
       <c r="O32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P32" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -2611,17 +2750,23 @@
       <c r="Y32" s="3">
         <v>0</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>0</v>
       </c>
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2629,79 +2774,85 @@
         <v>-4500</v>
       </c>
       <c r="E33" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="G33" s="3">
         <v>-5000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-5400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-4200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-3200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-4700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-3900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-3400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-2300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-4500</v>
-      </c>
-      <c r="N33" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-3500</v>
       </c>
       <c r="P33" s="3">
         <v>-4100</v>
       </c>
       <c r="Q33" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="R33" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="S33" s="3">
         <v>-2300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-2500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-2900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-1700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-2400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-500</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,8 +2931,14 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2789,164 +2946,176 @@
         <v>-4500</v>
       </c>
       <c r="E35" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="G35" s="3">
         <v>-5000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-5400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-4200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-3200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-4700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-3900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-3400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-2300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-4500</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-3500</v>
       </c>
       <c r="P35" s="3">
         <v>-4100</v>
       </c>
       <c r="Q35" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="R35" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="S35" s="3">
         <v>-2300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-2500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-2900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-1700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-2400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-500</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3144,10 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,74 +3176,76 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>7500</v>
+      </c>
+      <c r="F41" s="3">
         <v>8100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>13000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>18400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>21900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>25600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>28400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>32500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>37200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>39300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>43400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>46700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>51500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>54700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>61400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>81400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>19200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>20800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>23800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>600</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3085,59 +3258,65 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>20000</v>
+        <v>13300</v>
       </c>
       <c r="E42" s="3">
-        <v>20300</v>
+        <v>16500</v>
       </c>
       <c r="F42" s="3">
         <v>20000</v>
       </c>
       <c r="G42" s="3">
+        <v>20300</v>
+      </c>
+      <c r="H42" s="3">
+        <v>20000</v>
+      </c>
+      <c r="I42" s="3">
         <v>19400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>19400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>19500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>19100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>18000</v>
-      </c>
-      <c r="L42" s="3">
-        <v>18600</v>
-      </c>
-      <c r="M42" s="3">
-        <v>18800</v>
       </c>
       <c r="N42" s="3">
         <v>18600</v>
       </c>
       <c r="O42" s="3">
+        <v>18800</v>
+      </c>
+      <c r="P42" s="3">
+        <v>18600</v>
+      </c>
+      <c r="Q42" s="3">
         <v>19200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>19200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>18200</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3150,11 +3329,11 @@
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="3">
-        <v>0</v>
+      <c r="X42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z42" s="3">
         <v>0</v>
@@ -3165,37 +3344,43 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
+      <c r="E43" s="3">
+        <v>100</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3">
         <v>900</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -3245,8 +3430,14 @@
       <c r="AB43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3271,11 +3462,11 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3325,74 +3516,80 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
         <v>700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
+        <v>800</v>
+      </c>
+      <c r="K45" s="3">
         <v>700</v>
       </c>
-      <c r="H45" s="3">
-        <v>800</v>
-      </c>
-      <c r="I45" s="3">
-        <v>700</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1600</v>
-      </c>
-      <c r="K45" s="3">
-        <v>3500</v>
-      </c>
-      <c r="L45" s="3">
-        <v>4200</v>
       </c>
       <c r="M45" s="3">
         <v>3500</v>
       </c>
       <c r="N45" s="3">
+        <v>4200</v>
+      </c>
+      <c r="O45" s="3">
+        <v>3500</v>
+      </c>
+      <c r="P45" s="3">
         <v>2400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>2000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>2500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>2500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>1000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>1700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>1800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>100</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3405,74 +3602,80 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>25200</v>
+      </c>
+      <c r="F46" s="3">
         <v>29900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>35300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>39500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>43300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>47400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>51000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>55200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>58700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>62000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>65700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>67700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>72700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>76300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>82100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>82500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>20200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>22500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>25600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>800</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3485,8 +3688,14 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3511,11 +3720,11 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3565,59 +3774,65 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E48" s="3">
         <v>300</v>
       </c>
       <c r="F48" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G48" s="3">
         <v>300</v>
       </c>
       <c r="H48" s="3">
+        <v>200</v>
+      </c>
+      <c r="I48" s="3">
         <v>300</v>
-      </c>
-      <c r="I48" s="3">
-        <v>400</v>
       </c>
       <c r="J48" s="3">
         <v>300</v>
       </c>
       <c r="K48" s="3">
+        <v>400</v>
+      </c>
+      <c r="L48" s="3">
+        <v>300</v>
+      </c>
+      <c r="M48" s="3">
         <v>100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>100</v>
-      </c>
-      <c r="M48" s="3">
-        <v>200</v>
-      </c>
-      <c r="N48" s="3">
-        <v>200</v>
       </c>
       <c r="O48" s="3">
         <v>200</v>
       </c>
       <c r="P48" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>200</v>
+      </c>
+      <c r="R48" s="3">
         <v>300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>300</v>
       </c>
-      <c r="R48" s="3">
-        <v>0</v>
-      </c>
-      <c r="S48" s="3">
-        <v>0</v>
-      </c>
       <c r="T48" s="3">
         <v>0</v>
       </c>
@@ -3627,11 +3842,11 @@
       <c r="V48" s="3">
         <v>0</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+      <c r="X48" s="3">
+        <v>0</v>
       </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
@@ -3645,8 +3860,14 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3725,8 +3946,14 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +4032,14 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,8 +4118,14 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3918,41 +4157,41 @@
         <v>0</v>
       </c>
       <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
         <v>600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>1000</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
-      <c r="R52" s="3">
-        <v>0</v>
-      </c>
       <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3">
         <v>100</v>
       </c>
-      <c r="T52" s="3">
-        <v>0</v>
-      </c>
-      <c r="U52" s="3">
-        <v>0</v>
-      </c>
       <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+      <c r="X52" s="3">
         <v>300</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3965,8 +4204,14 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,74 +4290,80 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>25600</v>
+      </c>
+      <c r="F54" s="3">
         <v>30300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>35600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>39700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>43600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>47800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>51400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>55500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>58800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>62200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>66400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>68400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>74000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>77600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>82400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>82500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>20400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>22500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>25600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1000</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4125,8 +4376,14 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4412,10 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,74 +4444,76 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2500</v>
+        <v>4100</v>
       </c>
       <c r="E57" s="3">
         <v>2400</v>
       </c>
       <c r="F57" s="3">
-        <v>1600</v>
+        <v>2500</v>
       </c>
       <c r="G57" s="3">
-        <v>900</v>
+        <v>2400</v>
       </c>
       <c r="H57" s="3">
         <v>1600</v>
       </c>
       <c r="I57" s="3">
+        <v>900</v>
+      </c>
+      <c r="J57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K57" s="3">
         <v>1700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>2700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>3000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>5200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>2900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>2200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>400</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4265,8 +4526,14 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4289,14 +4556,14 @@
         <v>200</v>
       </c>
       <c r="J58" s="3">
+        <v>200</v>
+      </c>
+      <c r="K58" s="3">
+        <v>200</v>
+      </c>
+      <c r="L58" s="3">
         <v>100</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -4318,21 +4585,21 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
+      <c r="T58" s="3">
+        <v>0</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W58" s="3">
         <v>100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>100</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4345,71 +4612,77 @@
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F59" s="3">
         <v>900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1500</v>
-      </c>
-      <c r="K59" s="3">
-        <v>100</v>
-      </c>
-      <c r="L59" s="3">
-        <v>100</v>
       </c>
       <c r="M59" s="3">
         <v>100</v>
       </c>
       <c r="N59" s="3">
+        <v>100</v>
+      </c>
+      <c r="O59" s="3">
+        <v>100</v>
+      </c>
+      <c r="P59" s="3">
         <v>200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1600</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U59" s="3">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W59" s="3">
         <v>1700</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4425,74 +4698,80 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F60" s="3">
         <v>3600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>4600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>4000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>3000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2800</v>
-      </c>
-      <c r="L60" s="3">
-        <v>3100</v>
-      </c>
-      <c r="M60" s="3">
-        <v>5300</v>
       </c>
       <c r="N60" s="3">
         <v>3100</v>
       </c>
       <c r="O60" s="3">
+        <v>5300</v>
+      </c>
+      <c r="P60" s="3">
+        <v>3100</v>
+      </c>
+      <c r="Q60" s="3">
         <v>2300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>2700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>2300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>500</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4505,37 +4784,43 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
         <v>100</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G61" s="3">
         <v>100</v>
       </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>100</v>
-      </c>
-      <c r="I61" s="3">
-        <v>200</v>
       </c>
       <c r="J61" s="3">
         <v>100</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -4553,10 +4838,10 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T61" s="3">
         <v>100</v>
@@ -4565,10 +4850,10 @@
         <v>100</v>
       </c>
       <c r="V61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X61" s="3">
         <v>0</v>
@@ -4585,8 +4870,14 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4611,11 +4902,11 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -4624,19 +4915,19 @@
         <v>0</v>
       </c>
       <c r="O62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q62" s="3">
         <v>100</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
+      <c r="R62" s="3">
+        <v>100</v>
+      </c>
+      <c r="S62" s="3">
+        <v>100</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
@@ -4650,11 +4941,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>0</v>
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z62" s="3">
         <v>0</v>
@@ -4665,8 +4956,14 @@
       <c r="AB62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +5042,14 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +5128,14 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,74 +5214,80 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F66" s="3">
         <v>3700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>4000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>2700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>2400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>3200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>2800</v>
-      </c>
-      <c r="L66" s="3">
-        <v>3100</v>
-      </c>
-      <c r="M66" s="3">
-        <v>5300</v>
       </c>
       <c r="N66" s="3">
         <v>3100</v>
       </c>
       <c r="O66" s="3">
+        <v>5300</v>
+      </c>
+      <c r="P66" s="3">
+        <v>3100</v>
+      </c>
+      <c r="Q66" s="3">
         <v>2400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>2800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>2400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>500</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4985,8 +5300,14 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5336,10 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5418,14 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5504,14 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5255,8 +5590,14 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,74 +5676,80 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-80600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-76000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-70200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-65600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-60700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-55200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-51100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-47900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-43200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-39300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-35900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-33600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-29100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-25000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-21500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-17400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-15100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-12700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-9800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-8100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-7200</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5415,8 +5762,14 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5848,14 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5934,14 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,74 +6020,80 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>21200</v>
+      </c>
+      <c r="F76" s="3">
         <v>26600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>30900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>35800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>40900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>45400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>48300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>52600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>56000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>59000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>61100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>65300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>71600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>75700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>79600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>81700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>19700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>21600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>23200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>500</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5735,8 +6106,14 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,93 +6192,105 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5909,79 +6298,85 @@
         <v>-4500</v>
       </c>
       <c r="E81" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="F81" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="G81" s="3">
         <v>-5000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-5400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-4200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-3200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-4700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-3900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-3400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-2300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-4500</v>
-      </c>
-      <c r="N81" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-3500</v>
       </c>
       <c r="P81" s="3">
         <v>-4100</v>
       </c>
       <c r="Q81" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="R81" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="S81" s="3">
         <v>-2300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-2500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-2900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-1700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-2400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-500</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,8 +6405,10 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6019,20 +6416,20 @@
         <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
       </c>
       <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
         <v>100</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
       <c r="J83" s="3">
         <v>0</v>
       </c>
@@ -6081,17 +6478,23 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>0</v>
       </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6573,14 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6659,14 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6745,14 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6831,14 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,88 +6917,100 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="F89" s="3">
         <v>-5600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-5200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-3100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-3400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-3600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-3600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-3800</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-4000</v>
       </c>
       <c r="M89" s="3">
         <v>-2700</v>
       </c>
       <c r="N89" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="O89" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="P89" s="3">
         <v>-3300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-2000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-1700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-2100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-1600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-2900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-2100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-400</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,8 +7039,10 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6644,32 +7085,32 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
+      <c r="Y91" s="3">
+        <v>0</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
@@ -6680,8 +7121,14 @@
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +7207,14 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,76 +7293,82 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F94" s="3">
         <v>700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-1000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W94" s="3">
-        <v>0</v>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
+      <c r="Y94" s="3">
+        <v>0</v>
       </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
@@ -6920,8 +7379,14 @@
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,8 +7415,10 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6976,11 +7443,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7030,8 +7497,14 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7583,14 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7669,14 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,88 +7755,100 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-500</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>-2200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-900</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>64300</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>-100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>23700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>2900</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>1900</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7388,11 +7885,11 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
@@ -7406,11 +7903,11 @@
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-      <c r="V101" s="3">
-        <v>0</v>
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W101" s="3">
         <v>0</v>
@@ -7430,84 +7927,96 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F102" s="3">
         <v>-4900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-5400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-3600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-3600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-3400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-4100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-4700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-2100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-4100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-3300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-5300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-3100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-20000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>62100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-1600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-3000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>23200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>1400</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LTRN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LTRN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="92">
   <si>
     <t>LTRN</t>
   </si>
@@ -656,132 +656,136 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -812,8 +816,8 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -866,8 +870,11 @@
       <c r="AD8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -952,8 +959,11 @@
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1038,8 +1048,11 @@
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1070,94 +1083,98 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E12" s="3">
         <v>3300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>3900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>4300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1200</v>
-      </c>
-      <c r="T12" s="3">
-        <v>1300</v>
       </c>
       <c r="U12" s="3">
         <v>1300</v>
       </c>
       <c r="V12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="W12" s="3">
         <v>600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>200</v>
       </c>
-      <c r="AB12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1242,8 +1259,11 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1251,31 +1271,31 @@
         <v>3</v>
       </c>
       <c r="E14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F14" s="3">
         <v>200</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
@@ -1286,18 +1306,18 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3">
         <v>-100</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1313,8 +1333,8 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1328,8 +1348,11 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1414,8 +1437,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1443,180 +1469,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E17" s="3">
         <v>4800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>500</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-4800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-5900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-5400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-5700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-4900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-3500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-4100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-500</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1647,43 +1680,44 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E20" s="3">
+        <v>100</v>
+      </c>
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>-500</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="J20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L20" s="3">
         <v>-300</v>
       </c>
-      <c r="H20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-400</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-300</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>400</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-100</v>
       </c>
       <c r="O20" s="3">
         <v>-100</v>
@@ -1692,16 +1726,16 @@
         <v>-100</v>
       </c>
       <c r="Q20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S20" s="3">
         <v>100</v>
       </c>
       <c r="T20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U20" s="3">
         <v>0</v>
@@ -1724,8 +1758,8 @@
       <c r="AA20" s="3">
         <v>0</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
+      <c r="AB20" s="3">
+        <v>0</v>
       </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
@@ -1733,94 +1767,100 @@
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="G21" s="3">
         <v>-4700</v>
       </c>
-      <c r="E21" s="3">
-        <v>-5800</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-5100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-5600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-4500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-3400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-4900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-4000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-3400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-4500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-3500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-4100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-500</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1851,8 +1891,8 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1905,94 +1945,100 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-5400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-4200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-500</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2023,8 +2069,8 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -2077,8 +2123,11 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2163,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-5000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-4200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-500</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-5000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-500</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2421,8 +2479,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2507,8 +2568,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2593,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2679,43 +2746,46 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>200</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
+        <v>500</v>
+      </c>
+      <c r="H32" s="3">
+        <v>300</v>
+      </c>
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
-        <v>500</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="J32" s="3">
+        <v>400</v>
+      </c>
+      <c r="K32" s="3">
+        <v>100</v>
+      </c>
+      <c r="L32" s="3">
         <v>300</v>
       </c>
-      <c r="H32" s="3">
-        <v>100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>400</v>
-      </c>
-      <c r="J32" s="3">
-        <v>100</v>
-      </c>
-      <c r="K32" s="3">
-        <v>300</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-400</v>
-      </c>
-      <c r="N32" s="3">
-        <v>100</v>
       </c>
       <c r="O32" s="3">
         <v>100</v>
@@ -2724,16 +2794,16 @@
         <v>100</v>
       </c>
       <c r="Q32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S32" s="3">
         <v>-100</v>
       </c>
       <c r="T32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U32" s="3">
         <v>0</v>
@@ -2756,8 +2826,8 @@
       <c r="AA32" s="3">
         <v>0</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
+      <c r="AB32" s="3">
+        <v>0</v>
       </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
@@ -2765,94 +2835,100 @@
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-5000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-4200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-500</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2937,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-5000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-4200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-500</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3146,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3178,77 +3264,78 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E41" s="3">
         <v>6400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>13000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>18400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>21900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>25600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>28400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>32500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>37200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>39300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>43400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>46700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>51500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>54700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>61400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>81400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>19200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>20800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>23800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>600</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3264,62 +3351,65 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E42" s="3">
         <v>13300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>16500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>20000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>20300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>20000</v>
-      </c>
-      <c r="I42" s="3">
-        <v>19400</v>
       </c>
       <c r="J42" s="3">
         <v>19400</v>
       </c>
       <c r="K42" s="3">
+        <v>19400</v>
+      </c>
+      <c r="L42" s="3">
         <v>19500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>19100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>18000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>18600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>18800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>18600</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>19200</v>
       </c>
       <c r="R42" s="3">
         <v>19200</v>
       </c>
       <c r="S42" s="3">
+        <v>19200</v>
+      </c>
+      <c r="T42" s="3">
         <v>18200</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3335,8 +3425,8 @@
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z42" s="3">
-        <v>0</v>
+      <c r="Z42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA42" s="3">
         <v>0</v>
@@ -3350,40 +3440,43 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3">
         <v>100</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3">
         <v>900</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -3436,8 +3529,11 @@
       <c r="AD43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3468,8 +3564,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3522,77 +3618,80 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="D45" s="3">
+        <v>400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>500</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3">
         <v>700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>400</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2000</v>
-      </c>
-      <c r="R45" s="3">
-        <v>2500</v>
       </c>
       <c r="S45" s="3">
         <v>2500</v>
       </c>
       <c r="T45" s="3">
+        <v>2500</v>
+      </c>
+      <c r="U45" s="3">
         <v>1100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>100</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3608,77 +3707,80 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E46" s="3">
         <v>20800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>25200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>29900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>35300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>39500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>43300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>47400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>51000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>55200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>58700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>62000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>65700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>67700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>72700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>76300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>82100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>82500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>20200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>22500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>25600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>800</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3694,8 +3796,11 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3726,8 +3831,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3780,8 +3885,11 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3789,7 +3897,7 @@
         <v>200</v>
       </c>
       <c r="E48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F48" s="3">
         <v>300</v>
@@ -3798,28 +3906,28 @@
         <v>300</v>
       </c>
       <c r="H48" s="3">
+        <v>300</v>
+      </c>
+      <c r="I48" s="3">
         <v>200</v>
-      </c>
-      <c r="I48" s="3">
-        <v>300</v>
       </c>
       <c r="J48" s="3">
         <v>300</v>
       </c>
       <c r="K48" s="3">
+        <v>300</v>
+      </c>
+      <c r="L48" s="3">
         <v>400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>300</v>
-      </c>
-      <c r="M48" s="3">
-        <v>100</v>
       </c>
       <c r="N48" s="3">
         <v>100</v>
       </c>
       <c r="O48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P48" s="3">
         <v>200</v>
@@ -3828,13 +3936,13 @@
         <v>200</v>
       </c>
       <c r="R48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="S48" s="3">
         <v>300</v>
       </c>
       <c r="T48" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="U48" s="3">
         <v>0</v>
@@ -3848,8 +3956,8 @@
       <c r="X48" s="3">
         <v>0</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
+      <c r="Y48" s="3">
+        <v>0</v>
       </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
@@ -3866,8 +3974,11 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3952,8 +4063,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4038,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4124,8 +4241,11 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4163,38 +4283,38 @@
         <v>0</v>
       </c>
       <c r="O52" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="P52" s="3">
         <v>600</v>
       </c>
       <c r="Q52" s="3">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="R52" s="3">
         <v>1000</v>
       </c>
       <c r="S52" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T52" s="3">
         <v>0</v>
       </c>
       <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3">
         <v>100</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
-      </c>
       <c r="W52" s="3">
         <v>0</v>
       </c>
       <c r="X52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
         <v>300</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4210,8 +4330,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4296,77 +4419,80 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E54" s="3">
         <v>21100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>25600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>30300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>35600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>39700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>43600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>47800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>51400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>55500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>58800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>62200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>66400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>68400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>74000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>77600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>82400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>82500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>20400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>22500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>25600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1000</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4382,8 +4508,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4414,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4446,77 +4576,78 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4100</v>
+        <v>3400</v>
       </c>
       <c r="E57" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F57" s="3">
         <v>2400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>400</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4532,13 +4663,16 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E58" s="3">
         <v>200</v>
@@ -4562,11 +4696,11 @@
         <v>200</v>
       </c>
       <c r="L58" s="3">
+        <v>200</v>
+      </c>
+      <c r="M58" s="3">
         <v>100</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -4591,17 +4725,17 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W58" s="3">
-        <v>100</v>
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X58" s="3">
         <v>100</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
+      <c r="Y58" s="3">
+        <v>100</v>
       </c>
       <c r="Z58" s="3" t="s">
         <v>3</v>
@@ -4618,40 +4752,43 @@
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>3</v>
+      <c r="D59" s="3">
+        <v>1400</v>
       </c>
       <c r="E59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F59" s="3">
         <v>1700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1500</v>
-      </c>
-      <c r="M59" s="3">
-        <v>100</v>
       </c>
       <c r="N59" s="3">
         <v>100</v>
@@ -4660,32 +4797,32 @@
         <v>100</v>
       </c>
       <c r="P59" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q59" s="3">
         <v>200</v>
       </c>
       <c r="R59" s="3">
+        <v>200</v>
+      </c>
+      <c r="S59" s="3">
         <v>100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1600</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W59" s="3">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X59" s="3">
         <v>1700</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4704,77 +4841,80 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>4300</v>
+        <v>4900</v>
       </c>
       <c r="E60" s="3">
         <v>4300</v>
       </c>
       <c r="F60" s="3">
+        <v>4300</v>
+      </c>
+      <c r="G60" s="3">
         <v>3600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3000</v>
-      </c>
-      <c r="L60" s="3">
-        <v>2800</v>
       </c>
       <c r="M60" s="3">
         <v>2800</v>
       </c>
       <c r="N60" s="3">
+        <v>2800</v>
+      </c>
+      <c r="O60" s="3">
         <v>3100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>500</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,8 +4930,11 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4799,7 +4942,7 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3">
         <v>100</v>
@@ -4808,23 +4951,23 @@
         <v>100</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
         <v>100</v>
       </c>
       <c r="K61" s="3">
+        <v>100</v>
+      </c>
+      <c r="L61" s="3">
         <v>200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>100</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -4844,7 +4987,7 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U61" s="3">
         <v>100</v>
@@ -4856,7 +4999,7 @@
         <v>100</v>
       </c>
       <c r="X61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y61" s="3">
         <v>0</v>
@@ -4876,8 +5019,11 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4908,8 +5054,8 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
@@ -4921,7 +5067,7 @@
         <v>0</v>
       </c>
       <c r="Q62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R62" s="3">
         <v>100</v>
@@ -4929,8 +5075,8 @@
       <c r="S62" s="3">
         <v>100</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
+      <c r="T62" s="3">
+        <v>100</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
@@ -4947,8 +5093,8 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z62" s="3">
-        <v>0</v>
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA62" s="3">
         <v>0</v>
@@ -4962,8 +5108,11 @@
       <c r="AD62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5048,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5134,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5220,77 +5375,80 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E66" s="3">
         <v>4300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>500</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5306,8 +5464,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5338,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5424,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5510,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5596,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5682,77 +5853,80 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-84900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-80600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-76000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-70200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-65600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-60700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-55200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-51100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-47900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-43200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-39300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-35900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-33600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-29100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-25000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-21500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-17400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-15100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-12700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-9800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-8100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-7200</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5768,8 +5942,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5854,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5940,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6026,77 +6209,80 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E76" s="3">
         <v>16800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>21200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>26600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>30900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>35800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>40900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>45400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>48300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>52600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>56000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>59000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>61100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>65300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>71600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>75700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>79600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>81700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>19700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>21600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>23200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>500</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6112,8 +6298,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6198,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-5000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-4200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-500</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6407,8 +6605,9 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6416,11 +6615,11 @@
         <v>0</v>
       </c>
       <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
         <v>200</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
       <c r="G83" s="3">
         <v>0</v>
       </c>
@@ -6428,11 +6627,11 @@
         <v>0</v>
       </c>
       <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
         <v>100</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
       <c r="K83" s="3">
         <v>0</v>
       </c>
@@ -6484,8 +6683,8 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>3</v>
+      <c r="AB83" s="3">
+        <v>0</v>
       </c>
       <c r="AC83" s="3" t="s">
         <v>3</v>
@@ -6493,8 +6692,11 @@
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6579,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6665,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6751,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6837,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6923,85 +7137,88 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3400</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-3600</v>
       </c>
       <c r="K89" s="3">
         <v>-3600</v>
       </c>
       <c r="L89" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="M89" s="3">
         <v>-3800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-2100</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>-400</v>
       </c>
       <c r="AA89" s="3">
         <v>-400</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>3</v>
+      <c r="AB89" s="3">
+        <v>-400</v>
       </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
@@ -7009,8 +7226,11 @@
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7041,8 +7261,9 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7091,29 +7312,29 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
@@ -7127,8 +7348,11 @@
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7213,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7299,79 +7526,82 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E94" s="3">
         <v>3200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>3400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1000</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
+      <c r="W94" s="3">
+        <v>0</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>0</v>
       </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
@@ -7385,8 +7615,11 @@
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7417,8 +7650,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7449,8 +7683,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7503,8 +7737,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7589,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7675,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7761,16 +8004,19 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F100" s="3">
         <v>0</v>
@@ -7779,22 +8025,22 @@
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-500</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -7803,52 +8049,55 @@
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-900</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>64300</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>-100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>23700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2900</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>1900</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7891,8 +8140,8 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
+      <c r="Q101" s="3">
+        <v>0</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
@@ -7909,8 +8158,8 @@
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
+      <c r="W101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X101" s="3">
         <v>0</v>
@@ -7933,90 +8182,96 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5400</v>
-      </c>
-      <c r="H102" s="3">
-        <v>-3600</v>
       </c>
       <c r="I102" s="3">
         <v>-3600</v>
       </c>
       <c r="J102" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="K102" s="3">
         <v>-3400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-5700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-20000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>62100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-3000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>23200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1400</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LTRN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LTRN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="92">
   <si>
     <t>LTRN</t>
   </si>
@@ -656,140 +656,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AD7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -826,11 +833,11 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -880,8 +887,14 @@
       <c r="AF8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -972,8 +985,14 @@
       <c r="AF9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1064,8 +1083,14 @@
       <c r="AF10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,100 +1123,108 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F12" s="3">
         <v>2400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>3100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>3300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>4300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>3700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>3900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>4300</v>
-      </c>
-      <c r="K12" s="3">
-        <v>3600</v>
-      </c>
-      <c r="L12" s="3">
-        <v>2200</v>
       </c>
       <c r="M12" s="3">
         <v>3600</v>
       </c>
       <c r="N12" s="3">
+        <v>2200</v>
+      </c>
+      <c r="O12" s="3">
+        <v>3600</v>
+      </c>
+      <c r="P12" s="3">
         <v>2600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>2300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>3000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>2700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>2200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>3000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>1200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>1300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>1300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>1000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>200</v>
       </c>
-      <c r="AD12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,49 +1315,55 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>-200</v>
       </c>
-      <c r="G14" s="3">
-        <v>200</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="I14" s="3">
+        <v>100</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
@@ -1332,21 +1371,21 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W14" s="3">
         <v>-100</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1359,11 +1398,11 @@
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1374,8 +1413,14 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1511,14 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1548,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F17" s="3">
         <v>4300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>4700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>4800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>5900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>5200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>5400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>5700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>4900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>3500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>5200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>4300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>3800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>2100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>4400</v>
-      </c>
-      <c r="R17" s="3">
-        <v>4100</v>
-      </c>
-      <c r="S17" s="3">
-        <v>3500</v>
       </c>
       <c r="T17" s="3">
         <v>4100</v>
       </c>
       <c r="U17" s="3">
+        <v>3500</v>
+      </c>
+      <c r="V17" s="3">
+        <v>4100</v>
+      </c>
+      <c r="W17" s="3">
         <v>2400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>2500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>2900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>2400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>500</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-4300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-4700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-4800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-5900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-5200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-5400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-5700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-4900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-3500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-5200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-4300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-3800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-4400</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="S18" s="3">
-        <v>-3500</v>
       </c>
       <c r="T18" s="3">
         <v>-4100</v>
       </c>
       <c r="U18" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="V18" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="W18" s="3">
         <v>-2400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-2500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-2900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-500</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,71 +1780,73 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G20" s="3">
         <v>-200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
+        <v>100</v>
+      </c>
+      <c r="J20" s="3">
         <v>-500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-300</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-400</v>
       </c>
       <c r="L20" s="3">
         <v>-100</v>
       </c>
       <c r="M20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O20" s="3">
         <v>-300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>400</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-100</v>
       </c>
       <c r="R20" s="3">
         <v>-100</v>
       </c>
       <c r="S20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
@@ -1798,109 +1865,121 @@
       <c r="AC20" s="3">
         <v>0</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE20" s="3" t="s">
-        <v>3</v>
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>0</v>
       </c>
       <c r="AF20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="F21" s="3">
         <v>-4300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-4400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-4800</v>
       </c>
-      <c r="G21" s="3">
-        <v>-5800</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="J21" s="3">
         <v>-4700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-5100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-5600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-4500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-3400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-4900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-4000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-3400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-4500</v>
-      </c>
-      <c r="R21" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="S21" s="3">
-        <v>-3500</v>
       </c>
       <c r="T21" s="3">
         <v>-4100</v>
       </c>
       <c r="U21" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="V21" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="W21" s="3">
         <v>-2300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-2500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-2900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-500</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1937,11 +2016,11 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1991,100 +2070,112 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="F23" s="3">
         <v>-4200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-4300</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-5900</v>
       </c>
       <c r="H23" s="3">
         <v>-4500</v>
       </c>
       <c r="I23" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="K23" s="3">
         <v>-5000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-5400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-4200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-3200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-4700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-3900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-3400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-4500</v>
-      </c>
-      <c r="R23" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="S23" s="3">
-        <v>-3500</v>
       </c>
       <c r="T23" s="3">
         <v>-4100</v>
       </c>
       <c r="U23" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="V23" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="W23" s="3">
         <v>-2300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-2500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-2900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-500</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2121,11 +2212,11 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -2175,8 +2266,14 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2364,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="F26" s="3">
         <v>-4200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-4300</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-5900</v>
       </c>
       <c r="H26" s="3">
         <v>-4500</v>
       </c>
       <c r="I26" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="K26" s="3">
         <v>-5000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-5400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-4200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-3200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-4700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-3900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-3400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-4500</v>
-      </c>
-      <c r="R26" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-3500</v>
       </c>
       <c r="T26" s="3">
         <v>-4100</v>
       </c>
       <c r="U26" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="V26" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="W26" s="3">
         <v>-2300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-2500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-2900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-500</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="F27" s="3">
         <v>-4200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-4300</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-5900</v>
       </c>
       <c r="H27" s="3">
         <v>-4500</v>
       </c>
       <c r="I27" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="K27" s="3">
         <v>-5000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-5400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-4200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-3200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-4700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-3900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-3400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-4500</v>
-      </c>
-      <c r="R27" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-3500</v>
       </c>
       <c r="T27" s="3">
         <v>-4100</v>
       </c>
       <c r="U27" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="V27" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="W27" s="3">
         <v>-2300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-2500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-2900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-500</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2658,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2756,14 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2854,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,71 +2952,77 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
+        <v>100</v>
+      </c>
+      <c r="G32" s="3">
         <v>200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
-        <v>100</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J32" s="3">
         <v>500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>300</v>
-      </c>
-      <c r="J32" s="3">
-        <v>100</v>
-      </c>
-      <c r="K32" s="3">
-        <v>400</v>
       </c>
       <c r="L32" s="3">
         <v>100</v>
       </c>
       <c r="M32" s="3">
+        <v>400</v>
+      </c>
+      <c r="N32" s="3">
+        <v>100</v>
+      </c>
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-400</v>
-      </c>
-      <c r="P32" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>100</v>
       </c>
       <c r="R32" s="3">
         <v>100</v>
       </c>
       <c r="S32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T32" s="3">
+        <v>100</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
@@ -2902,109 +3041,121 @@
       <c r="AC32" s="3">
         <v>0</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE32" s="3" t="s">
-        <v>3</v>
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>0</v>
       </c>
       <c r="AF32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="F33" s="3">
         <v>-4200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-4300</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-5900</v>
       </c>
       <c r="H33" s="3">
         <v>-4500</v>
       </c>
       <c r="I33" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="K33" s="3">
         <v>-5000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-5400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-4200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-3200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-4700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-3900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-3400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-4500</v>
-      </c>
-      <c r="R33" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-3500</v>
       </c>
       <c r="T33" s="3">
         <v>-4100</v>
       </c>
       <c r="U33" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="V33" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="W33" s="3">
         <v>-2300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-2500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-2900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-500</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3246,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="F35" s="3">
         <v>-4200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-4300</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-5900</v>
       </c>
       <c r="H35" s="3">
         <v>-4500</v>
       </c>
       <c r="I35" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="K35" s="3">
         <v>-5000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-5400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-4200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-3200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-4700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-3900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-3400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-4500</v>
-      </c>
-      <c r="R35" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-3500</v>
       </c>
       <c r="T35" s="3">
         <v>-4100</v>
       </c>
       <c r="U35" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="V35" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="W35" s="3">
         <v>-2300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-2500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-2900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-500</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AD38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3487,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,86 +3523,88 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F41" s="3">
         <v>8400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>6100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>6400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>7500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>8100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>13000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>18400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>21900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>25600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>28400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>32500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>37200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>39300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>43400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>46700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>51500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>54700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>61400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>81400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>19200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>20800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>23800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>600</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3444,71 +3617,77 @@
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E42" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F42" s="3">
         <v>4000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>9800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>13300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>16500</v>
-      </c>
-      <c r="H42" s="3">
-        <v>20000</v>
-      </c>
-      <c r="I42" s="3">
-        <v>20300</v>
       </c>
       <c r="J42" s="3">
         <v>20000</v>
       </c>
       <c r="K42" s="3">
+        <v>20300</v>
+      </c>
+      <c r="L42" s="3">
+        <v>20000</v>
+      </c>
+      <c r="M42" s="3">
         <v>19400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>19400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>19500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>19100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>18000</v>
-      </c>
-      <c r="P42" s="3">
-        <v>18600</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>18800</v>
       </c>
       <c r="R42" s="3">
         <v>18600</v>
       </c>
       <c r="S42" s="3">
+        <v>18800</v>
+      </c>
+      <c r="T42" s="3">
+        <v>18600</v>
+      </c>
+      <c r="U42" s="3">
         <v>19200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>19200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>18200</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3521,11 +3700,11 @@
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC42" s="3">
-        <v>0</v>
+      <c r="AB42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD42" s="3">
         <v>0</v>
@@ -3536,49 +3715,55 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
+      <c r="E43" s="3">
+        <v>0</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3">
         <v>900</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -3628,8 +3813,14 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3666,11 +3857,11 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3720,86 +3911,92 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>200</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E45" s="3">
         <v>400</v>
       </c>
       <c r="F45" s="3">
+        <v>200</v>
+      </c>
+      <c r="G45" s="3">
+        <v>400</v>
+      </c>
+      <c r="H45" s="3">
         <v>500</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
+        <v>800</v>
+      </c>
+      <c r="J45" s="3">
         <v>700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>400</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1600</v>
-      </c>
-      <c r="O45" s="3">
-        <v>3500</v>
-      </c>
-      <c r="P45" s="3">
-        <v>4200</v>
       </c>
       <c r="Q45" s="3">
         <v>3500</v>
       </c>
       <c r="R45" s="3">
+        <v>4200</v>
+      </c>
+      <c r="S45" s="3">
+        <v>3500</v>
+      </c>
+      <c r="T45" s="3">
         <v>2400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>2000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>2500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>2500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>1100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>1000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>1700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>1800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>100</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3812,86 +4009,92 @@
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>10800</v>
+      </c>
+      <c r="F46" s="3">
         <v>13500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>17200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>20800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>25200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>29900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>35300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>39500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>43300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>47400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>51000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>55200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>58700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>62000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>65700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>67700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>72700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>76300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>82100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>82500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>20200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>22500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>25600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>800</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3904,8 +4107,14 @@
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3942,11 +4151,11 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3996,8 +4205,14 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4005,62 +4220,62 @@
         <v>100</v>
       </c>
       <c r="E48" s="3">
+        <v>100</v>
+      </c>
+      <c r="F48" s="3">
+        <v>100</v>
+      </c>
+      <c r="G48" s="3">
         <v>200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>200</v>
-      </c>
-      <c r="G48" s="3">
-        <v>300</v>
-      </c>
-      <c r="H48" s="3">
-        <v>300</v>
       </c>
       <c r="I48" s="3">
         <v>300</v>
       </c>
       <c r="J48" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K48" s="3">
         <v>300</v>
       </c>
       <c r="L48" s="3">
+        <v>200</v>
+      </c>
+      <c r="M48" s="3">
         <v>300</v>
-      </c>
-      <c r="M48" s="3">
-        <v>400</v>
       </c>
       <c r="N48" s="3">
         <v>300</v>
       </c>
       <c r="O48" s="3">
+        <v>400</v>
+      </c>
+      <c r="P48" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q48" s="3">
         <v>100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>100</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>200</v>
-      </c>
-      <c r="R48" s="3">
-        <v>200</v>
       </c>
       <c r="S48" s="3">
         <v>200</v>
       </c>
       <c r="T48" s="3">
+        <v>200</v>
+      </c>
+      <c r="U48" s="3">
+        <v>200</v>
+      </c>
+      <c r="V48" s="3">
         <v>300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>300</v>
       </c>
-      <c r="V48" s="3">
-        <v>0</v>
-      </c>
-      <c r="W48" s="3">
-        <v>0</v>
-      </c>
       <c r="X48" s="3">
         <v>0</v>
       </c>
@@ -4070,11 +4285,11 @@
       <c r="Z48" s="3">
         <v>0</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB48" s="3" t="s">
-        <v>3</v>
+      <c r="AA48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB48" s="3">
+        <v>0</v>
       </c>
       <c r="AC48" s="3" t="s">
         <v>3</v>
@@ -4088,8 +4303,14 @@
       <c r="AF48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4180,8 +4401,14 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4499,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,8 +4597,14 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4409,41 +4648,41 @@
         <v>0</v>
       </c>
       <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
         <v>600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>1000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>1000</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
-      </c>
-      <c r="V52" s="3">
-        <v>0</v>
-      </c>
       <c r="W52" s="3">
+        <v>0</v>
+      </c>
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
         <v>100</v>
       </c>
-      <c r="X52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>0</v>
-      </c>
       <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="3">
         <v>300</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4456,8 +4695,14 @@
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,86 +4793,92 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>11000</v>
+      </c>
+      <c r="F54" s="3">
         <v>13600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>17400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>21100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>25600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>30300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>35600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>39700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>43600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>47800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>51400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>55500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>58800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>62200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>66400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>68400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>74000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>77600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>82400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>82500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>20400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>22500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>25600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1000</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4640,8 +4891,14 @@
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4931,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,86 +4967,88 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E57" s="3">
         <v>3100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
+        <v>3100</v>
+      </c>
+      <c r="G57" s="3">
         <v>3400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2900</v>
-      </c>
-      <c r="G57" s="3">
-        <v>2400</v>
-      </c>
-      <c r="H57" s="3">
-        <v>2500</v>
       </c>
       <c r="I57" s="3">
         <v>2400</v>
       </c>
       <c r="J57" s="3">
-        <v>1600</v>
+        <v>2500</v>
       </c>
       <c r="K57" s="3">
-        <v>900</v>
+        <v>2400</v>
       </c>
       <c r="L57" s="3">
         <v>1600</v>
       </c>
       <c r="M57" s="3">
+        <v>900</v>
+      </c>
+      <c r="N57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="O57" s="3">
         <v>1700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>2700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>3000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>5200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>2900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>2200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>1600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>1100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>400</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4800,8 +5061,14 @@
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4812,10 +5079,10 @@
         <v>100</v>
       </c>
       <c r="F58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H58" s="3">
         <v>200</v>
@@ -4836,14 +5103,14 @@
         <v>200</v>
       </c>
       <c r="N58" s="3">
+        <v>200</v>
+      </c>
+      <c r="O58" s="3">
+        <v>200</v>
+      </c>
+      <c r="P58" s="3">
         <v>100</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -4865,21 +5132,21 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
+      <c r="X58" s="3">
+        <v>0</v>
       </c>
       <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA58" s="3">
         <v>100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>100</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4892,83 +5159,89 @@
       <c r="AF58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>900</v>
+      <c r="D59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E59" s="3">
         <v>1400</v>
       </c>
       <c r="F59" s="3">
+        <v>900</v>
+      </c>
+      <c r="G59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H59" s="3">
         <v>1200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1500</v>
-      </c>
-      <c r="O59" s="3">
-        <v>100</v>
-      </c>
-      <c r="P59" s="3">
-        <v>100</v>
       </c>
       <c r="Q59" s="3">
         <v>100</v>
       </c>
       <c r="R59" s="3">
+        <v>100</v>
+      </c>
+      <c r="S59" s="3">
+        <v>100</v>
+      </c>
+      <c r="T59" s="3">
         <v>200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1600</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA59" s="3">
         <v>1700</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4984,86 +5257,92 @@
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F60" s="3">
         <v>4000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>4900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>4300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>4300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>4600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>4000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>2300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>3000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>2800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>2800</v>
-      </c>
-      <c r="P60" s="3">
-        <v>3100</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>5300</v>
       </c>
       <c r="R60" s="3">
         <v>3100</v>
       </c>
       <c r="S60" s="3">
+        <v>5300</v>
+      </c>
+      <c r="T60" s="3">
+        <v>3100</v>
+      </c>
+      <c r="U60" s="3">
         <v>2300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>2700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>2300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>500</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5076,8 +5355,14 @@
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5091,34 +5376,34 @@
         <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
         <v>100</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K61" s="3">
         <v>100</v>
       </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>100</v>
-      </c>
-      <c r="M61" s="3">
-        <v>200</v>
       </c>
       <c r="N61" s="3">
         <v>100</v>
       </c>
       <c r="O61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q61" s="3">
         <v>0</v>
@@ -5136,10 +5421,10 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X61" s="3">
         <v>100</v>
@@ -5148,10 +5433,10 @@
         <v>100</v>
       </c>
       <c r="Z61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB61" s="3">
         <v>0</v>
@@ -5168,8 +5453,14 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5206,11 +5497,11 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
-      <c r="P62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q62" s="3">
         <v>0</v>
@@ -5219,19 +5510,19 @@
         <v>0</v>
       </c>
       <c r="S62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U62" s="3">
         <v>100</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
+      <c r="V62" s="3">
+        <v>100</v>
+      </c>
+      <c r="W62" s="3">
+        <v>100</v>
       </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
@@ -5245,11 +5536,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC62" s="3">
-        <v>0</v>
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD62" s="3">
         <v>0</v>
@@ -5260,8 +5551,14 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5649,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5747,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,86 +5845,92 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F66" s="3">
         <v>4000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>4300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>4400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>3700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>4700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>4000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>2700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>2400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>3200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>2900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>2800</v>
-      </c>
-      <c r="P66" s="3">
-        <v>3100</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>5300</v>
       </c>
       <c r="R66" s="3">
         <v>3100</v>
       </c>
       <c r="S66" s="3">
+        <v>5300</v>
+      </c>
+      <c r="T66" s="3">
+        <v>3100</v>
+      </c>
+      <c r="U66" s="3">
         <v>2400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>2800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>2400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>500</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5628,8 +5943,14 @@
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5983,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +6077,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6175,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6273,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,86 +6371,92 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-96500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-93100</v>
+      </c>
+      <c r="F72" s="3">
         <v>-89100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-84900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-80600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-76000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-70200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-65600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-60700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-55200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-51100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-47900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-43200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-39300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-35900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-33600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-29100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-25000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-21500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-17400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-15100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-12700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-8100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-7200</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6122,8 +6469,14 @@
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6567,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6665,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,86 +6763,92 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>6500</v>
+      </c>
+      <c r="F76" s="3">
         <v>9600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>12500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>16800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>21200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>26600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>30900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>35800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>40900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>45400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>48300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>52600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>56000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>59000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>61100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>65300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>71600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>75700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>79600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>81700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>19700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>21600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>23200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>500</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6490,8 +6861,14 @@
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6959,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AD80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="F81" s="3">
         <v>-4200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-4300</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-5900</v>
       </c>
       <c r="H81" s="3">
         <v>-4500</v>
       </c>
       <c r="I81" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="K81" s="3">
         <v>-5000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-5400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-4200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-3200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-4700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-3900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-3400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-4500</v>
-      </c>
-      <c r="R81" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-3500</v>
       </c>
       <c r="T81" s="3">
         <v>-4100</v>
       </c>
       <c r="U81" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="V81" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="W81" s="3">
         <v>-2300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-2500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-2900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-500</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,41 +7200,43 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
       </c>
       <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
         <v>200</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
       <c r="J83" s="3">
         <v>0</v>
       </c>
       <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
         <v>100</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
       <c r="N83" s="3">
         <v>0</v>
       </c>
@@ -6888,17 +7285,23 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE83" s="3" t="s">
-        <v>3</v>
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="3">
+        <v>0</v>
       </c>
       <c r="AF83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7392,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7490,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7588,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7686,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7784,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="F89" s="3">
         <v>-4600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-3900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-4400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-4000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-5600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-5200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-3100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-3400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-3600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-3600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-3800</v>
-      </c>
-      <c r="O89" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-4000</v>
       </c>
       <c r="Q89" s="3">
         <v>-2700</v>
       </c>
       <c r="R89" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="S89" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="T89" s="3">
         <v>-3300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-2000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-4700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-1700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-2100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-1600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-400</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,13 +7922,15 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -7539,32 +7980,32 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>0</v>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>3</v>
+      <c r="AC91" s="3">
+        <v>0</v>
       </c>
       <c r="AD91" s="3" t="s">
         <v>3</v>
@@ -7575,8 +8016,14 @@
       <c r="AF91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +8114,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,88 +8212,94 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F94" s="3">
         <v>5900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>3600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>3200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>3400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-1000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-1000</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA94" s="3">
-        <v>0</v>
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>3</v>
+      <c r="AC94" s="3">
+        <v>0</v>
       </c>
       <c r="AD94" s="3" t="s">
         <v>3</v>
@@ -7851,8 +8310,14 @@
       <c r="AF94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8350,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7923,11 +8390,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7977,8 +8444,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8542,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8640,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,100 +8738,112 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3">
+        <v>500</v>
+      </c>
+      <c r="F100" s="3">
         <v>1000</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-500</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>-2200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-900</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>64300</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>23700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>2900</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>1900</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8354,7 +8851,7 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
@@ -8395,11 +8892,11 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
       </c>
       <c r="U101" s="3" t="s">
         <v>3</v>
@@ -8413,11 +8910,11 @@
       <c r="X101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>0</v>
+      <c r="Y101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA101" s="3">
         <v>0</v>
@@ -8437,96 +8934,108 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="F102" s="3">
         <v>2300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-4900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-5400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-3600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-3600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-3400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-4100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-4700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-2100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-3300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-5300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-3100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-5700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-20000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>62100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-1600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>23200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>1400</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
